--- a/output/resultado_cotizaciones.xlsx
+++ b/output/resultado_cotizaciones.xlsx
@@ -1,85 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b6ffb6eb20c50b6/Escritorio/Equipo_04_COMII/output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_2B59D2BFD3305893CE73F5924D1510344D07F7B8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{148336DD-C8F4-4E95-AC39-2FDD04BCAC63}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
-  <si>
-    <t>Producto</t>
-  </si>
-  <si>
-    <t>Proveedor</t>
-  </si>
-  <si>
-    <t>Precio</t>
-  </si>
-  <si>
-    <t>PlazoEntrega</t>
-  </si>
-  <si>
-    <t>CondicionesPago</t>
-  </si>
-  <si>
-    <t>Score_Precio</t>
-  </si>
-  <si>
-    <t>Score_Tiempo</t>
-  </si>
-  <si>
-    <t>Score_Pago</t>
-  </si>
-  <si>
-    <t>Score_Total</t>
-  </si>
-  <si>
-    <t>Laptop Core i5</t>
-  </si>
-  <si>
-    <t>TecnoStore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CompuGlobal </t>
-  </si>
-  <si>
-    <t>Impresora MultiFuncional</t>
-  </si>
-  <si>
-    <t>OfficeMax</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -98,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,163 +408,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PlazoEntrega</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CondicionesPago</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Score_Precio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Score_Tiempo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score_Pago</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Score_Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Laptop Core i5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TecnoStore</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>650</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="G2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Laptop Core i5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CompuGlobal </t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>620</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.769230769230766</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.769230769230766</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Impresora MultiFuncional</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TecnoStore</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>180</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43.38461538461539</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>70.88461538461539</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Impresora MultiFuncional</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OfficeMax</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>195</v>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>650</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>12.5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>620</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
+      <c r="E5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
         <v>15</v>
       </c>
-      <c r="F3">
-        <v>2.7692307692307661</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>7.7692307692307656</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>180</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>43.384615384615387</v>
-      </c>
-      <c r="G4">
-        <v>17.5</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>70.884615384615387</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>195</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>45</v>
-      </c>
-      <c r="F5">
-        <v>42</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>15</v>
-      </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>77</v>
       </c>
     </row>

--- a/output/resultado_cotizaciones.xlsx
+++ b/output/resultado_cotizaciones.xlsx
@@ -122,6 +122,146 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Puntaje promedio por proveedor</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sheet1'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sheet1'!$K$2:$K$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sheet1'!$L$2:$L$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Puntaje promedio</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Proveedor</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +602,16 @@
           <t>Score_Total</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Puntaje promedio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -484,16 +634,24 @@
         <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>32.14285714285714</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I2" t="n">
-        <v>22.5</v>
+        <v>60.47619047619047</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>TecnoStore</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>73.31785714285714</v>
       </c>
     </row>
     <row r="3">
@@ -517,16 +675,24 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>2.769230769230766</v>
+        <v>33.42857142857143</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>7.769230769230766</v>
+        <v>53.8452380952381</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CompuGlobal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>37.36904761904762</v>
       </c>
     </row>
     <row r="4">
@@ -550,16 +716,24 @@
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>43.38461538461539</v>
+        <v>52.28571428571428</v>
       </c>
       <c r="G4" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>70.88461538461539</v>
+        <v>82.28571428571428</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>OfficeMax</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>53.94642857142858</v>
       </c>
     </row>
     <row r="5">
@@ -583,19 +757,571 @@
         <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>51.64285714285715</v>
       </c>
       <c r="G5" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>86.22619047619048</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Computadoras S.A</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>59.40476190476191</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Laptop i17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Computadoras S.A</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>850</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>59.40476190476191</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>TechElSalvador</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>64.09523809523809</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Laptop i17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TechElSalvador</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>820</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24.85714285714285</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>52.77380952380952</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Importadora SV</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>89.8452380952381</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Monitor 27"</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TechElSalvador</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>175</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.16666666666666</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I8" t="n">
+        <v>75.41666666666666</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GlobalTech</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>88.11309523809524</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Monitor 27"</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Importadora SV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>130</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45</v>
+      </c>
+      <c r="F9" t="n">
+        <v>54.42857142857143</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>89.8452380952381</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>CompraMax</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>88.125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Teclado y Mouse Inalámbrico</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GlobalTech</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" t="n">
+        <v>58.07142857142857</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>87.23809523809524</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Inversiones Digitales</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>84.94761904761904</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Teclado y Mouse Inalámbrico</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CompraMax</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>58.71428571428572</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>92.46428571428572</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>DataSytem</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>32.32142857142858</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Teclado y Mouse Inalámbrico</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inversiones Digitales</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Teclado y Mouse Inalámbrico</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TecnoStore</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" t="n">
         <v>20</v>
       </c>
-      <c r="H5" t="n">
+      <c r="E13" t="n">
         <v>15</v>
       </c>
-      <c r="I5" t="n">
-        <v>77</v>
+      <c r="F13" t="n">
+        <v>58.62857142857143</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>70.71190476190476</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Servidor NAS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CompuGlobal </t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I14" t="n">
+        <v>20.89285714285714</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Servidor NAS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OfficeMax</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>21.66666666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Servidor NAS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DataSytem </t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>45</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.571428571428575</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I16" t="n">
+        <v>32.32142857142858</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Monitor 24"</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Inversiones Digitales</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>130</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" t="n">
+        <v>54.42857142857143</v>
+      </c>
+      <c r="G17" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>83.5952380952381</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Monitor 24"</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GlobalTech</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>150</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>45</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53.57142857142858</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I18" t="n">
+        <v>88.98809523809524</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monitor 24"</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CompraMax</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>145</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" t="n">
+        <v>53.78571428571428</v>
+      </c>
+      <c r="G19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>83.78571428571428</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Monitor 24"</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TecnoStore</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>170</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" t="n">
+        <v>52.71428571428572</v>
+      </c>
+      <c r="G20" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I20" t="n">
+        <v>79.79761904761905</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>